--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.00034</v>
+        <v>17.18572</v>
       </c>
       <c r="D2" t="n">
-        <v>16.75409</v>
+        <v>16.61434</v>
       </c>
       <c r="E2" t="n">
-        <v>17.12383</v>
+        <v>16.68374</v>
       </c>
       <c r="F2" t="n">
-        <v>42.88686</v>
+        <v>42.30526</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05075</v>
+        <v>0.05148</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80437</v>
+        <v>1.86403</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.71529</v>
+        <v>16.98341</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7263</v>
+        <v>16.69187</v>
       </c>
       <c r="E3" t="n">
-        <v>17.20426</v>
+        <v>16.87992</v>
       </c>
       <c r="F3" t="n">
-        <v>43.25614</v>
+        <v>42.93739</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05021</v>
+        <v>0.05212</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85126</v>
+        <v>1.82865</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.21834</v>
+        <v>17.33511</v>
       </c>
       <c r="D4" t="n">
-        <v>16.74628</v>
+        <v>16.38693</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76248</v>
+        <v>16.73844</v>
       </c>
       <c r="F4" t="n">
-        <v>44.02454</v>
+        <v>43.58639</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05063</v>
+        <v>0.05144</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84016</v>
+        <v>1.84673</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63459</v>
+        <v>17.04345</v>
       </c>
       <c r="D6" t="n">
-        <v>15.88406</v>
+        <v>16.34447</v>
       </c>
       <c r="E6" t="n">
-        <v>16.71965</v>
+        <v>16.40723</v>
       </c>
       <c r="F6" t="n">
-        <v>21.97969</v>
+        <v>21.80504</v>
       </c>
       <c r="G6" t="n">
-        <v>34.31136</v>
+        <v>35.0996</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.92619</v>
+        <v>17.17379</v>
       </c>
       <c r="D7" t="n">
-        <v>16.08965</v>
+        <v>16.21258</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32887</v>
+        <v>16.82785</v>
       </c>
       <c r="F7" t="n">
-        <v>22.01817</v>
+        <v>22.11711</v>
       </c>
       <c r="G7" t="n">
-        <v>33.97405</v>
+        <v>34.35336</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.01087</v>
+        <v>17.22293</v>
       </c>
       <c r="D8" t="n">
-        <v>16.15195</v>
+        <v>16.11477</v>
       </c>
       <c r="E8" t="n">
-        <v>16.48934</v>
+        <v>16.66524</v>
       </c>
       <c r="F8" t="n">
-        <v>21.86756</v>
+        <v>21.92877</v>
       </c>
       <c r="G8" t="n">
-        <v>34.42686</v>
+        <v>34.40608</v>
       </c>
     </row>
   </sheetData>
